--- a/_data_list/Field_Force_Sample_RY.xlsx
+++ b/_data_list/Field_Force_Sample_RY.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EMIL\OneDrive\Desktop\OrangeFlow\_data_list\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Telegram_Project\OrangeFlow_Dev\_data_list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1107956-B8A9-47A9-89DE-0EFF3388B04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0ADBE92-6124-4A54-8229-C0D625C97D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AJ$9</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="121">
   <si>
     <t>DMS_CODE</t>
   </si>
@@ -204,6 +207,201 @@
   </si>
   <si>
     <t>MER-RYZBRB0107</t>
+  </si>
+  <si>
+    <t>Nahedul Islam</t>
+  </si>
+  <si>
+    <t>DBBL</t>
+  </si>
+  <si>
+    <t>Bhairab</t>
+  </si>
+  <si>
+    <t>090480193</t>
+  </si>
+  <si>
+    <t>Komolpur</t>
+  </si>
+  <si>
+    <t>Siam</t>
+  </si>
+  <si>
+    <t>Brother</t>
+  </si>
+  <si>
+    <t>SSC</t>
+  </si>
+  <si>
+    <t>Kamalpur Hazi Zahir Uddin High School</t>
+  </si>
+  <si>
+    <t>O+</t>
+  </si>
+  <si>
+    <t>Purbo Komolpur, Bhairab, Kishoreganj.</t>
+  </si>
+  <si>
+    <t>Deloar Hossain</t>
+  </si>
+  <si>
+    <t>Nahida Begum</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>MER-RYZBRB0126</t>
+  </si>
+  <si>
+    <t>R647080</t>
+  </si>
+  <si>
+    <t>Faisol Alam</t>
+  </si>
+  <si>
+    <t>Vobanipur</t>
+  </si>
+  <si>
+    <t>Nazma</t>
+  </si>
+  <si>
+    <t>Wife</t>
+  </si>
+  <si>
+    <t>HSC</t>
+  </si>
+  <si>
+    <t>Shimulkandi College</t>
+  </si>
+  <si>
+    <t>B+</t>
+  </si>
+  <si>
+    <t>Vobanipur Rosulpur, Shimulkandi, Bhairab, Kishoreganj.</t>
+  </si>
+  <si>
+    <t>Musa Mia</t>
+  </si>
+  <si>
+    <t>Sayera Begum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobayer </t>
+  </si>
+  <si>
+    <t>Kakina, Kaliganj, Lalmonirhat</t>
+  </si>
+  <si>
+    <t>Md. Abul Kashem</t>
+  </si>
+  <si>
+    <t>Mst. Ayesha Khatun</t>
+  </si>
+  <si>
+    <t>MER-RYZBRB0127</t>
+  </si>
+  <si>
+    <t>R647134</t>
+  </si>
+  <si>
+    <t>Sumon</t>
+  </si>
+  <si>
+    <t>AB+</t>
+  </si>
+  <si>
+    <t>Ahamod Hossain</t>
+  </si>
+  <si>
+    <t>Momjahan Begum</t>
+  </si>
+  <si>
+    <t>Elongjuri, Itna, Kishoreganj</t>
+  </si>
+  <si>
+    <t>RCC1404</t>
+  </si>
+  <si>
+    <t>Islam</t>
+  </si>
+  <si>
+    <t>Mostofa</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>Md Jafor Ullah</t>
+  </si>
+  <si>
+    <t>Sajuda Begum</t>
+  </si>
+  <si>
+    <t>Ibrahimpur Narayenpur, Belobo, Narsingdi.</t>
+  </si>
+  <si>
+    <t>RCC1161</t>
+  </si>
+  <si>
+    <t>Arman</t>
+  </si>
+  <si>
+    <t>A-</t>
+  </si>
+  <si>
+    <t>Md Jasim Uddin</t>
+  </si>
+  <si>
+    <t>Josna Begum</t>
+  </si>
+  <si>
+    <t>Koylag, Bajitpur, Kishoreganj</t>
+  </si>
+  <si>
+    <t>RCC1163</t>
+  </si>
+  <si>
+    <t>DBBL Agent</t>
+  </si>
+  <si>
+    <t>7017344002631</t>
+  </si>
+  <si>
+    <t>Ajmina</t>
+  </si>
+  <si>
+    <t>Amir Uddin</t>
+  </si>
+  <si>
+    <t>Safia Begum</t>
+  </si>
+  <si>
+    <t>Kalikaproshad, Bhairab, Kishoreganj.</t>
+  </si>
+  <si>
+    <t>RCC1406</t>
+  </si>
+  <si>
+    <t>RCC0554</t>
+  </si>
+  <si>
+    <t>RCC0546</t>
+  </si>
+  <si>
+    <t>Nayan Mia</t>
+  </si>
+  <si>
+    <t>B-</t>
+  </si>
+  <si>
+    <t>Md Alal Uddin</t>
+  </si>
+  <si>
+    <t>Rabeya Khatun</t>
+  </si>
+  <si>
+    <t>Bhairabpur, Bhairab, Kishoreganj.</t>
   </si>
 </sst>
 </file>
@@ -263,18 +461,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -573,44 +797,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AJ13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="35.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="39.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="8" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="41.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="21" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -668,7 +891,7 @@
       <c r="R1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="3" t="s">
         <v>16</v>
       </c>
       <c r="T1" s="1" t="s">
@@ -684,25 +907,25 @@
         <v>20</v>
       </c>
       <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>28</v>
@@ -723,214 +946,750 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G2">
+      <c r="F2" s="5">
+        <v>1786080093</v>
+      </c>
+      <c r="G2" s="5">
         <v>1410678746</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="K2" s="2">
+      <c r="I2" s="5">
+        <v>10000</v>
+      </c>
+      <c r="K2" s="6">
         <v>46082</v>
       </c>
-      <c r="N2" s="2">
+      <c r="M2" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N2" s="6">
         <v>33834</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="7">
         <v>6404733260</v>
       </c>
-      <c r="Q2" s="3"/>
-      <c r="AJ2" t="s">
+      <c r="P2" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>1731580493357</v>
+      </c>
+      <c r="S2" s="8"/>
+      <c r="U2" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="V2" s="5">
+        <v>1752787879</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC2" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD2" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ2" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="5">
         <v>1410071973</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="K3" s="2">
+      <c r="I3" s="5">
+        <v>10000</v>
+      </c>
+      <c r="K3" s="6">
         <v>46082</v>
       </c>
-      <c r="N3" s="2">
+      <c r="M3" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N3" s="6">
         <v>32540</v>
       </c>
-      <c r="O3" s="3">
+      <c r="O3" s="7">
         <v>1314935507162</v>
       </c>
-      <c r="Q3" s="3"/>
-      <c r="AJ3" t="s">
+      <c r="P3" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>1731580492738</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="S3" s="8"/>
+      <c r="U3" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="V3" s="5">
+        <v>1864929394</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB3" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC3" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AD3" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ3" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="5">
         <v>1410240211</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="2">
+      <c r="I4" s="5">
+        <v>10000</v>
+      </c>
+      <c r="K4" s="6">
         <v>45971</v>
       </c>
-      <c r="N4" s="2">
+      <c r="M4" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N4" s="6">
         <v>1</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O4" s="7">
         <v>2863545949</v>
       </c>
-      <c r="Q4" s="3"/>
-      <c r="AJ4" t="s">
+      <c r="P4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>1731050292189</v>
+      </c>
+      <c r="S4" s="8"/>
+      <c r="U4" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="V4" s="5">
+        <v>1407911493</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC4" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD4" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ4" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="5">
         <v>1410436602</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="K5" s="2">
+      <c r="I5" s="5">
+        <v>10000</v>
+      </c>
+      <c r="K5" s="6">
         <v>45971</v>
       </c>
-      <c r="N5" s="2">
+      <c r="M5" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N5" s="6">
         <v>31595</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="7">
         <v>4813347971938</v>
       </c>
-      <c r="Q5" s="3"/>
-      <c r="AJ5" t="s">
+      <c r="P5" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>2311580489016</v>
+      </c>
+      <c r="S5" s="8"/>
+      <c r="U5" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="V5" s="5">
+        <v>1730797404</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA5" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC5" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD5" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ5" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="5">
         <v>1410213723</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="K6" s="2">
+      <c r="I6" s="5">
+        <v>10000</v>
+      </c>
+      <c r="K6" s="6">
         <v>46054</v>
       </c>
-      <c r="N6" s="2">
+      <c r="M6" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N6" s="6">
         <v>38161</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O6" s="7">
         <v>1042040244</v>
       </c>
-      <c r="Q6" s="3"/>
-      <c r="AJ6" t="s">
+      <c r="P6" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>2311580512005</v>
+      </c>
+      <c r="S6" s="8"/>
+      <c r="U6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="V6" s="5">
+        <v>1782371767</v>
+      </c>
+      <c r="W6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA6" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AB6" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="AD6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="AE6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ6" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B7" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="5">
         <v>1410173774</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="2">
+      <c r="I7" s="5">
+        <v>10000</v>
+      </c>
+      <c r="K7" s="6">
         <v>46054</v>
       </c>
-      <c r="N7" s="2">
+      <c r="M7" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N7" s="6">
         <v>33970</v>
       </c>
-      <c r="O7" s="3">
+      <c r="O7" s="7">
         <v>2824445262</v>
       </c>
-      <c r="Q7" s="3"/>
-      <c r="AJ7" t="s">
+      <c r="P7" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="S7" s="8"/>
+      <c r="U7" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="V7" s="5">
+        <v>1925717710</v>
+      </c>
+      <c r="W7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z7" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA7" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB7" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="AC7" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AD7" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ7" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="K8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="3"/>
-      <c r="Q8" s="3"/>
+    <row r="8" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1763122889</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1410720313</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I8" s="5">
+        <v>10000</v>
+      </c>
+      <c r="K8" s="6">
+        <v>46143</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N8" s="6">
+        <v>36906</v>
+      </c>
+      <c r="O8" s="7">
+        <v>8263476999</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>1731580441218</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="S8" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="T8" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="U8" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="V8" s="5">
+        <v>1325533299</v>
+      </c>
+      <c r="W8" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="X8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z8" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ8" s="5" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="K9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="3"/>
-      <c r="Q9" s="3"/>
+    <row r="9" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1984397910</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1410031485</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="5">
+        <v>10000</v>
+      </c>
+      <c r="K9" s="6">
+        <v>46143</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N9" s="6">
+        <v>31902</v>
+      </c>
+      <c r="O9" s="7">
+        <v>5546839951</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="S9" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="T9" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="U9" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="V9" s="5">
+        <v>1812206330</v>
+      </c>
+      <c r="W9" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="X9" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z9" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB9" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC9" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD9" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ9" s="5" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="K10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="3"/>
-      <c r="Q10" s="3"/>
+    <row r="10" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="S10" s="8"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="O11" s="3"/>
+    <row r="11" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O11" s="7"/>
+      <c r="S11" s="8"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="O12" s="3"/>
+    <row r="12" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O12" s="7"/>
+      <c r="S12" s="8"/>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="O13" s="3"/>
+      <c r="O13" s="2"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="Q1:Q1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
